--- a/data/trans_orig/IP74A3_2023-Provincia-trans_orig.xlsx
+++ b/data/trans_orig/IP74A3_2023-Provincia-trans_orig.xlsx
@@ -535,7 +535,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Adulto según si ha resuelto las cuotas de compras aplazadas en 2023 (tasa de respuesta: 100,0%)</t>
+          <t>Adultos según si tienen resuelto el retraso en los pagos de cuotas de compras aplazadas en 2023 (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -800,12 +800,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>621</t>
+          <t>490</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>4856</t>
+          <t>4579</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -815,12 +815,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>12,78%</t>
+          <t>10,1%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>100,0%</t>
+          <t>94,29%</t>
         </is>
       </c>
     </row>
@@ -913,12 +913,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>291</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>4337</t>
+          <t>4419</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -928,12 +928,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>5,98%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>89,3%</t>
+          <t>91,01%</t>
         </is>
       </c>
     </row>
@@ -2788,12 +2788,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>364</t>
+          <t>340</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>3987</t>
+          <t>4172</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2803,12 +2803,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>7,52%</t>
+          <t>7,02%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>82,39%</t>
+          <t>86,21%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2823,12 +2823,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>527</t>
+          <t>473</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>4457</t>
+          <t>4520</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2838,12 +2838,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>10,98%</t>
+          <t>9,85%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>92,89%</t>
+          <t>94,21%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2858,12 +2858,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>1985</t>
+          <t>1830</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>7772</t>
+          <t>7590</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2873,12 +2873,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>20,6%</t>
+          <t>18,98%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>80,63%</t>
+          <t>78,74%</t>
         </is>
       </c>
     </row>
@@ -2901,12 +2901,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>866</t>
+          <t>666</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>4480</t>
+          <t>4498</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2916,12 +2916,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>17,88%</t>
+          <t>13,77%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>92,56%</t>
+          <t>92,93%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -2936,12 +2936,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>287</t>
+          <t>286</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>4254</t>
+          <t>4328</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2951,12 +2951,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>5,99%</t>
+          <t>5,96%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>88,67%</t>
+          <t>90,2%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2971,12 +2971,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>1867</t>
+          <t>2049</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>7654</t>
+          <t>7809</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -2986,12 +2986,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>19,37%</t>
+          <t>21,26%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>79,4%</t>
+          <t>81,02%</t>
         </is>
       </c>
     </row>
